--- a/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>This dictionary defines quantities produced or consumed by a rigid inclusion design that are carried as parameters rather than as schema elements. Two kinds of entry are present. The first are the method-specific arching coefficients, which exist only inside one named arching model and are carried in the coefficient property of a diggs:ArchingCoefficients object; each is conditioned on the arching model that defines it, so a file reporting a Hewlett-Randolph efficiency under a Zaeske design does not validate. The second are design quantities that are common to several practices and are carried in the otherProperty escape hatch of diggs:RIColumnDesignType or diggs:RILTPDesignType, whichever the quantity belongs to. Quantities that every arching practice ultimately produces - the stress delivered to the column head and the stress reaching the soil between heads - are deliberately NOT here: they are typed elements on diggs:RILTPDesignType, because they are the two values on which designs prepared under different standards can actually be compared.</t>
+          <t>This dictionary defines quantities produced or consumed by a rigid inclusion design that are carried as parameters rather than as fixed schema elements. Two kinds of entry are present. The first are the method-specific arching coefficients, which exist only inside one named arching model and are carried in the coefficient property of a diggs:ArchingCoefficients object; each is conditioned on the arching model that defines it, so a file reporting a Hewlett-Randolph efficiency under a Zaeske design does not validate. The second are design quantities that are common to several practices or vary too freely to justify a fixed schema element - the geometry and stiffness ratios that gate whether an arching method's unit-cell idealisation applies to a given layout, open-ended since a future method may add its own - carried in diggs:RISystemDesignType/methodApplicabilityRatio. The active earth pressure coefficient, once considered for this dictionary, turned out not to need it: a single, always-the-same-formula quantity, now the typed element diggs:RILTPDesignType/activeEarthPressureCoefficient instead. Quantities that every arching practice ultimately produces - the stress delivered to the column head and the stress reaching the soil between heads - are deliberately NOT here: they are typed elements on diggs:RILTPDesignType, because they are the two values on which designs prepared under different standards can actually be compared.</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -1392,22 +1392,22 @@
     </row>
     <row r="11">
       <c r="A11" s="2">
-        <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>active_earth_pressure_coefficient</t>
+          <t>arching_height_ratio</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Active earth pressure coefficient</t>
+          <t>Arching height ratio</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>The active earth pressure coefficient Ka = tan^2(45 deg - phi'/2) of the embankment fill, used in the lateral thrust and lateral spreading checks. Unlike the arching coefficients in this dictionary it is not tied to any one arching model, so it is carried as a general design property rather than inside a diggs:ArchingCoefficients object.</t>
+          <t>The geometric ratio h/(s-d) of platform or embankment height above the inclusion heads to the clear spacing between inclusions. One of the geometric limits that determine whether a given arching method is applicable to a given layout; a method used outside the ratio range it was validated over is not defensible, which is what makes this worth stating rather than leaving to be recomputed.</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -1417,43 +1417,43 @@
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>pressure per pressure</t>
+          <t>length per length</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>BS 8006-1:2010+A1:2016</t>
+          <t>EBGEO (DGGT), Chapter 6.9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2">
-        <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2953,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>equivalent_diameter</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Equivalent tributary diameter</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>The diameter dErs (EBGEO) or De (FHWA) of the equivalent circular unit cell assigned to one inclusion - the circle of equal area to the tributary area the inclusion supports. Derived from the spacing and grid pattern, and reported because the unit-cell radius rather than the centre-to-centre spacing is what enters most arching and settlement formulations.</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+          <t>diameter_spacing_ratio</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>Diameter to spacing ratio</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>The geometric ratio d/s of inclusion diameter to centre-to-centre spacing. A second method-applicability limit, and the quantity most directly related to the area replacement ratio; carry both rather than either alone, since practices state their limits against different ones of the two.</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
-        <is>
-          <t>length</t>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>length per length</t>
         </is>
       </c>
       <c r="G12" s="9" t="inlineStr">
@@ -1464,68 +1464,68 @@
     </row>
     <row r="13">
       <c r="A13" s="2">
-        <f>IF(ISNA(VLOOKUP(B13,AssociatedElements!B$2:B2951,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2954,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>column_axial_utilization</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>Column axial utilization</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>The ratio N/Rc of axial demand on an inclusion to its structural axial resistance. Reported as a ratio of two forces rather than as a dimensionless number so that the quantity class records what is being compared; a utilization above unity is a failed check, which is why the quantity is worth carrying explicitly rather than leaving a reader to divide two other reported values.</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+          <t>spacing_aspect_ratio</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Spacing aspect ratio</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>The ratio sx/sy of the two orthogonal centre-to-centre spacings of a rectangular grid. Unity for a square grid. Methods derived for square or triangular layouts carry limits on how far from unity this may go before the unit-cell idealisation stops holding.</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>force per force</t>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>length per length</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>ASIRI National Project Recommendations (IREX)</t>
+          <t>EBGEO (DGGT), Chapter 6.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2">
-        <f>IF(ISNA(VLOOKUP(B14,AssociatedElements!B$2:B2952,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2955,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>arching_height_ratio</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Arching height ratio</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>The geometric ratio h/(s-d) of platform or embankment height above the inclusion heads to the clear spacing between inclusions. One of the geometric limits that determine whether a given arching method is applicable to a given layout; a method used outside the ratio range it was validated over is not defensible, which is what makes this worth stating rather than leaving to be recomputed.</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+          <t>stiffness_ratio</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>Subgrade stiffness ratio</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>The ratio ks,T/ks of the stiffness of the improved composite ground to that of the untreated ground, used by EBGEO as a gate on whether its method may be applied. THE GATE VALUE IS NOT STATED HERE. The threshold this ratio must exceed is a pass/fail requirement on method validity, not a design value, and belongs in a diggs:DesignConformanceCriterion that names this property. That keeps the requirement where a reviewer looks for requirements and lets it differ by project or edition. The commonly cited threshold has not been verified against a retrievable clause; the criterion carrying it should cite its own source.</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>double</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>length per length</t>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1536,115 +1536,43 @@
     </row>
     <row r="15">
       <c r="A15" s="2">
-        <f>IF(ISNA(VLOOKUP(B15,AssociatedElements!B$2:B2953,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>diameter_spacing_ratio</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>Diameter to spacing ratio</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>The geometric ratio d/s of inclusion diameter to centre-to-centre spacing. A second method-applicability limit, and the quantity most directly related to the area replacement ratio; carry both rather than either alone, since practices state their limits against different ones of the two.</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>length per length</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>EBGEO (DGGT), Chapter 6.9</t>
-        </is>
-      </c>
+        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B15" s="13" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="19" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <f>IF(ISNA(VLOOKUP(B16,AssociatedElements!B$2:B2954,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>spacing_aspect_ratio</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>Spacing aspect ratio</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>The ratio sx/sy of the two orthogonal centre-to-centre spacings of a rectangular grid. Unity for a square grid. Methods derived for square or triangular layouts carry limits on how far from unity this may go before the unit-cell idealisation stops holding.</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>length per length</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>EBGEO (DGGT), Chapter 6.9</t>
-        </is>
-      </c>
+        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B16" s="13" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="19" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <f>IF(ISNA(VLOOKUP(B17,AssociatedElements!B$2:B2955,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>stiffness_ratio</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>Subgrade stiffness ratio</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>The ratio ks,T/ks of the stiffness of the improved composite ground to that of the untreated ground, used by EBGEO as a gate on whether its method may be applied. THE GATE VALUE IS NOT STATED HERE. The threshold this ratio must exceed is a pass/fail requirement on method validity, not a design value, and belongs in a diggs:DesignConformanceCriterion that names this property. That keeps the requirement where a reviewer looks for requirements and lets it differ by project or edition. The commonly cited threshold has not been verified against a retrievable clause; the criterion carrying it should cite its own source.</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>double</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>dimensionless</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>EBGEO (DGGT), Chapter 6.9</t>
-        </is>
-      </c>
+        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B17" s="13" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="19" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B18" s="13" t="n"/>
@@ -1656,7 +1584,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B19" s="13" t="n"/>
@@ -1668,7 +1596,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B20" s="13" t="n"/>
@@ -1680,121 +1608,121 @@
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="19" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="D21" s="16" t="n"/>
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B22" s="13" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="19" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="13" t="n"/>
       <c r="G22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B23" s="13" t="n"/>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="13" t="n"/>
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="D24" s="16" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B24" s="13" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="13" t="n"/>
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B25" s="13" t="n"/>
       <c r="C25" s="13" t="n"/>
+      <c r="D25" s="14" t="n"/>
       <c r="E25" s="13" t="n"/>
       <c r="F25" s="13" t="n"/>
       <c r="G25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B26" s="13" t="n"/>
       <c r="C26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
       <c r="E26" s="13" t="n"/>
       <c r="F26" s="13" t="n"/>
       <c r="G26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B27" s="13" t="n"/>
       <c r="C27" s="13" t="n"/>
-      <c r="D27" s="15" t="n"/>
+      <c r="D27" s="14" t="n"/>
       <c r="E27" s="13" t="n"/>
       <c r="F27" s="13" t="n"/>
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B28" s="13" t="n"/>
-      <c r="C28" s="13" t="n"/>
-      <c r="D28" s="14" t="n"/>
-      <c r="E28" s="13" t="n"/>
-      <c r="F28" s="13" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="19" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
       <c r="G28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="19" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
       <c r="G29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B30" s="13" t="n"/>
-      <c r="C30" s="13" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="13" t="n"/>
-      <c r="F30" s="13" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
       <c r="G30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B31" s="13" t="n"/>
@@ -1806,7 +1734,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B32" s="13" t="n"/>
@@ -1818,7 +1746,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B33" s="13" t="n"/>
@@ -1830,46 +1758,10 @@
     </row>
     <row r="34">
       <c r="A34" s="2">
-        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B34" s="13" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="19" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
       <c r="G34" s="9" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2">
-        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="9" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="18" t="n"/>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="9" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2">
-        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="G37" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1886,7 +1778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -2108,12 +2000,12 @@
     </row>
     <row r="11">
       <c r="A11">
-        <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>active_earth_pressure_coefficient</t>
+          <t>arching_height_ratio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2123,18 +2015,18 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ancestor::diggs:RILTPDesign</t>
+          <t>ancestor::diggs:methodApplicabilityRatio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>equivalent_diameter</t>
+        <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>diameter_spacing_ratio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2144,18 +2036,18 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ancestor::diggs:RIColumnDesign</t>
+          <t>ancestor::diggs:methodApplicabilityRatio</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <f>IF(ISNA(VLOOKUP(B13,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>column_axial_utilization</t>
+        <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>spacing_aspect_ratio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2165,18 +2057,18 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ancestor::diggs:RIColumnDesign</t>
+          <t>ancestor::diggs:methodApplicabilityRatio</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <f>IF(ISNA(VLOOKUP(B14,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>arching_height_ratio</t>
+        <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>stiffness_ratio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2186,212 +2078,149 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ancestor::diggs:RIColumnDesign</t>
+          <t>ancestor::diggs:methodApplicabilityRatio</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <f>IF(ISNA(VLOOKUP(B15,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>diameter_spacing_ratio</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>//diggs:parameterName</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ancestor::diggs:RIColumnDesign</t>
-        </is>
-      </c>
+        <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16">
-        <f>IF(ISNA(VLOOKUP(B16,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>spacing_aspect_ratio</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>//diggs:parameterName</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ancestor::diggs:RIColumnDesign</t>
-        </is>
-      </c>
+        <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B16" s="20" t="n"/>
     </row>
     <row r="17">
       <c r="A17">
-        <f>IF(ISNA(VLOOKUP(B17,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>stiffness_ratio</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>//diggs:parameterName</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ancestor::diggs:RIColumnDesign</t>
-        </is>
-      </c>
+        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18">
-        <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B18" s="2" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B18" s="20" t="n"/>
     </row>
     <row r="19">
       <c r="A19">
-        <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20">
-        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B20" s="20" t="n"/>
     </row>
     <row r="21">
       <c r="A21">
-        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B21" s="20" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22">
-        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B22" s="20" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23">
-        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B23" s="20" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24">
-        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B24" s="2" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25">
-        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B25" s="2" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26">
-        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B26" s="2" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27">
-        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28">
-        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29">
-        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30">
-        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31">
-        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B31" s="13" t="n"/>
     </row>
     <row r="32">
       <c r="A32">
-        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="A33">
-        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B33" s="13" t="n"/>
     </row>
     <row r="34">
       <c r="A34">
-        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B34" s="13" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B35" s="13" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B36" s="13" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37">
         <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B37" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>This dictionary defines quantities produced or consumed by a rigid inclusion design that are carried as parameters rather than as fixed schema elements. Two kinds of entry are present. The first are the method-specific arching coefficients, which exist only inside one named arching model and are carried in the coefficient property of a diggs:ArchingCoefficients object; each is conditioned on the arching model that defines it, so a file reporting a Hewlett-Randolph efficiency under a Zaeske design does not validate. The second are design quantities that are common to several practices or vary too freely to justify a fixed schema element - the geometry and stiffness ratios that gate whether an arching method's unit-cell idealisation applies to a given layout, open-ended since a future method may add its own - carried in diggs:RISystemDesignType/methodApplicabilityRatio. The active earth pressure coefficient, once considered for this dictionary, turned out not to need it: a single, always-the-same-formula quantity, now the typed element diggs:RILTPDesignType/activeEarthPressureCoefficient instead. Quantities that every arching practice ultimately produces - the stress delivered to the column head and the stress reaching the soil between heads - are deliberately NOT here: they are typed elements on diggs:RILTPDesignType, because they are the two values on which designs prepared under different standards can actually be compared.</t>
+          <t>This dictionary defines quantities produced or consumed by a rigid inclusion design that are carried as parameters rather than as fixed schema elements. Two kinds of entry are present. The first are the method-specific arching coefficients, which exist only inside one named arching model and are carried in the coefficient property of a diggs:ArchingCoefficients object; each is conditioned on the arching model that defines it, so a file reporting a Hewlett-Randolph efficiency under a Zaeske design does not validate. The second are design quantities that are common to several practices or vary too freely to justify a fixed schema element - the geometry and stiffness ratios that gate whether an arching method's unit-cell idealisation applies to a given layout, open-ended since a future method may add its own - carried in diggs:RITreatedAreaDesignType/methodApplicabilityRatio. The active earth pressure coefficient, once considered for this dictionary, turned out not to need it: a single, always-the-same-formula quantity, now the typed element diggs:RILTPDesignType/activeEarthPressureCoefficient instead. Quantities that every arching practice ultimately produces - the stress delivered to the column head and the stress reaching the soil between heads - are deliberately NOT here: they are typed elements on diggs:RILTPDesignType, because they are the two values on which designs prepared under different standards can actually be compared.</t>
         </is>
       </c>
     </row>

--- a/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
@@ -1539,12 +1539,36 @@
         <f>IF(ISNA(VLOOKUP(B18,AssociatedElements!B$2:B2956,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B15" s="13" t="n"/>
-      <c r="C15" s="18" t="n"/>
-      <c r="D15" s="19" t="n"/>
-      <c r="E15" s="18" t="n"/>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="9" t="n"/>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>stress_reduction_ratio</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Stress reduction ratio (SRR)</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>The ratio of the vertical stress carried by the soft soil between inclusion heads to the vertical stress that would act there without arching. FHWA GEC-13 Eq 3-23.</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>double</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>FHWA GEC-13 (FHWA-NHI-16-028)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2">
@@ -2087,7 +2111,21 @@
         <f>IF(ISNA(VLOOKUP(B18,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B15" s="2" t="n"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>stress_reduction_ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>//diggs:parameterName</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ancestor::diggs:ArchingCoefficients/diggs:archingModel[.='fhwa_parabolic']</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16">

--- a/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/ri_design_properties.xlsx
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="7" customWidth="1" style="2" min="1" max="1"/>
@@ -1572,7 +1572,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2">
-        <f>IF(ISNA(VLOOKUP(B19,AssociatedElements!B$2:B2957,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B16" s="13" t="n"/>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2">
-        <f>IF(ISNA(VLOOKUP(B20,AssociatedElements!B$2:B2958,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B17" s="13" t="n"/>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2">
-        <f>IF(ISNA(VLOOKUP(B21,AssociatedElements!B$2:B2959,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B18" s="13" t="n"/>
@@ -1608,7 +1608,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2">
-        <f>IF(ISNA(VLOOKUP(B22,AssociatedElements!B$2:B2960,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B19" s="13" t="n"/>
@@ -1620,27 +1620,26 @@
     </row>
     <row r="20">
       <c r="A20" s="2">
-        <f>IF(ISNA(VLOOKUP(B23,AssociatedElements!B$2:B2961,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="D20" s="16" t="n"/>
       <c r="G20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2">
-        <f>IF(ISNA(VLOOKUP(B24,AssociatedElements!B$2:B2962,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="D21" s="16" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
       <c r="G21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2">
-        <f>IF(ISNA(VLOOKUP(B25,AssociatedElements!B$2:B2963,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B22" s="13" t="n"/>
@@ -1651,30 +1650,31 @@
     </row>
     <row r="23">
       <c r="A23" s="2">
-        <f>IF(ISNA(VLOOKUP(B26,AssociatedElements!B$2:B2964,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B23" s="13" t="n"/>
       <c r="C23" s="13" t="n"/>
+      <c r="D23" s="15" t="n"/>
       <c r="E23" s="13" t="n"/>
       <c r="F23" s="13" t="n"/>
       <c r="G23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2">
-        <f>IF(ISNA(VLOOKUP(B27,AssociatedElements!B$2:B2965,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B24" s="13" t="n"/>
       <c r="C24" s="13" t="n"/>
-      <c r="D24" s="15" t="n"/>
+      <c r="D24" s="14" t="n"/>
       <c r="E24" s="13" t="n"/>
       <c r="F24" s="13" t="n"/>
       <c r="G24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2">
-        <f>IF(ISNA(VLOOKUP(B28,AssociatedElements!B$2:B2966,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B25" s="13" t="n"/>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2">
-        <f>IF(ISNA(VLOOKUP(B29,AssociatedElements!B$2:B2967,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B26" s="13" t="n"/>
@@ -1698,19 +1698,19 @@
     </row>
     <row r="27">
       <c r="A27" s="2">
-        <f>IF(ISNA(VLOOKUP(B30,AssociatedElements!B$2:B2968,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="14" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="19" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
       <c r="G27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2">
-        <f>IF(ISNA(VLOOKUP(B31,AssociatedElements!B$2:B2969,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B28" s="13" t="n"/>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2">
-        <f>IF(ISNA(VLOOKUP(B32,AssociatedElements!B$2:B2970,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B29" s="13" t="n"/>
@@ -1734,7 +1734,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2">
-        <f>IF(ISNA(VLOOKUP(B33,AssociatedElements!B$2:B2971,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B30" s="13" t="n"/>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2">
-        <f>IF(ISNA(VLOOKUP(B34,AssociatedElements!B$2:B2972,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B31" s="13" t="n"/>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2">
-        <f>IF(ISNA(VLOOKUP(B35,AssociatedElements!B$2:B2973,1,FALSE)),"Not used","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
       <c r="B32" s="13" t="n"/>
@@ -1770,22 +1770,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2">
-        <f>IF(ISNA(VLOOKUP(B36,AssociatedElements!B$2:B2974,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
+        <v/>
+      </c>
       <c r="G33" s="9" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <f>IF(ISNA(VLOOKUP(B37,AssociatedElements!B$2:B2975,1,FALSE)),"Not used","")</f>
-        <v/>
-      </c>
-      <c r="G34" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1802,7 +1790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
     <col width="6.83203125" customWidth="1" min="1" max="1"/>
@@ -2129,136 +2117,129 @@
     </row>
     <row r="16">
       <c r="A16">
-        <f>IF(ISNA(VLOOKUP(B19,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B16" s="20" t="n"/>
     </row>
     <row r="17">
       <c r="A17">
-        <f>IF(ISNA(VLOOKUP(B20,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18">
-        <f>IF(ISNA(VLOOKUP(B21,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B18" s="20" t="n"/>
     </row>
     <row r="19">
       <c r="A19">
-        <f>IF(ISNA(VLOOKUP(B22,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B19" s="20" t="n"/>
     </row>
     <row r="20">
       <c r="A20">
-        <f>IF(ISNA(VLOOKUP(B23,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B20" s="20" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21">
-        <f>IF(ISNA(VLOOKUP(B24,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B21" s="2" t="n"/>
     </row>
     <row r="22">
       <c r="A22">
-        <f>IF(ISNA(VLOOKUP(B25,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B22" s="2" t="n"/>
     </row>
     <row r="23">
       <c r="A23">
-        <f>IF(ISNA(VLOOKUP(B26,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B23" s="2" t="n"/>
+        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <v/>
+      </c>
+      <c r="B23" s="13" t="n"/>
     </row>
     <row r="24">
       <c r="A24">
-        <f>IF(ISNA(VLOOKUP(B27,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B24" s="13" t="n"/>
     </row>
     <row r="25">
       <c r="A25">
-        <f>IF(ISNA(VLOOKUP(B28,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B25" s="13" t="n"/>
     </row>
     <row r="26">
       <c r="A26">
-        <f>IF(ISNA(VLOOKUP(B29,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B26" s="13" t="n"/>
     </row>
     <row r="27">
       <c r="A27">
-        <f>IF(ISNA(VLOOKUP(B30,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B27" s="13" t="n"/>
     </row>
     <row r="28">
       <c r="A28">
-        <f>IF(ISNA(VLOOKUP(B31,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B28" s="13" t="n"/>
     </row>
     <row r="29">
       <c r="A29">
-        <f>IF(ISNA(VLOOKUP(B32,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B29" s="13" t="n"/>
     </row>
     <row r="30">
       <c r="A30">
-        <f>IF(ISNA(VLOOKUP(B33,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B30" s="13" t="n"/>
     </row>
     <row r="31">
       <c r="A31">
-        <f>IF(ISNA(VLOOKUP(B34,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B31" s="13" t="n"/>
     </row>
     <row r="32">
       <c r="A32">
-        <f>IF(ISNA(VLOOKUP(B35,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
+        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
       <c r="B32" s="13" t="n"/>
     </row>
     <row r="33">
       <c r="A33">
-        <f>IF(ISNA(VLOOKUP(B36,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
-        <v/>
-      </c>
-      <c r="B33" s="13" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34">
         <f>IF(ISNA(VLOOKUP(B37,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B34" s="2" t="n"/>
+      <c r="B33" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
